--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261014.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>144,921</t>
+          <t>800,897</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>800,897</t>
+          <t>144,921</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,445,981</t>
+          <t>1,184,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,184,441</t>
+          <t>3,445,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>1,297,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,297,384</t>
+          <t>144,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>768,000</t>
+          <t>492,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>492,000</t>
+          <t>2,168,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2,168,107</t>
+          <t>768,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>287,000</t>
+          <t>316,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>316,000</t>
+          <t>287,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>4,910,956</t>
+          <t>751,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>751,000</t>
+          <t>4,910,956</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>1,740,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,740,000</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>251,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>673,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>251,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>673,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
